--- a/2026/ЗАВОДЫ/Останкино/Лог данные сочинские (СЫРЫ).xlsx
+++ b/2026/ЗАВОДЫ/Останкино/Лог данные сочинские (СЫРЫ).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\altair.strelets\docs\ХОЛДИНГ\ОСТАНКИНО МОЛОКО\22. Симбирева\Симбирева\Лог данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9528D91E-6FF5-4B6F-B13C-73B119CAF905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0263ED21-1A35-4BD6-B23C-9BB49EFC4DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>№</t>
   </si>
@@ -133,6 +133,12 @@
     <t>2+6</t>
   </si>
   <si>
+    <t xml:space="preserve">БЖП "Балык" копч.  РЕЗ. 4 вкуса </t>
+  </si>
+  <si>
+    <t>Сыр "Косичка"  копч. МИНИ</t>
+  </si>
+  <si>
     <t>ПАПА МОЖЕТ</t>
   </si>
   <si>
@@ -146,10 +152,6 @@
   </si>
   <si>
     <t>СТО 0154559873-009-2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">белки – 25,8 г, жиры – 19,2 г, углеводы – 0 г.
-Энергетическая ценность/калорийность: 1161 кДж/277 </t>
   </si>
   <si>
     <t>белки – 25,8 г, жиры – 19,2 г, углеводы – 0 г.
@@ -162,20 +164,26 @@
     <t>1d033e12-57d6-4a32-a680-7ab84e0a14dc</t>
   </si>
   <si>
-    <t>БЖП произведенный по технологии сыра копченый "Балык" резаный 4 вкуса</t>
-  </si>
-  <si>
-    <t>БЖП произведенный по технологии сыра копченый "Косичка" мини Ассорти</t>
-  </si>
-  <si>
-    <t>Сыр копченый "Косичка" мини ПАПА МОЖЕТ 55г лоток</t>
+    <t>БЖП "Косичка" копч.  МИНИ Ассорти 100г (лоток, 10шт/кор)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">жиры – 22,1 г; белки – 19,6 г; углеводы – 0 г. </t>
+  </si>
+  <si>
+    <t>сыр обезжиренный (молоко обезжиренное пастеризованное, закваска из чистых культур мезофильных молочнокислых микроорганизмов, молокосвертывающий фермент (пепсин животного происхождения), уплотнитель - кальций хлористый), масло сливочное, соль пищевая.происхождения), кальций хлористый (уплотнитель)</t>
+  </si>
+  <si>
+    <t>сыр обезжиренный (молоко обезжиренное пастеризованное, закваска из чистых культур мезофильных молочнокислых микро-организмов, молокосвертывающий фермент (пепсин животного происхождения), уплотнитель - кальций хлористый), заменитель молочного жира (рафинированные дезодорированные растительные масла в натуральном и модифицированном виде (пальмовое и его фракции, подсолнечное, рапсовое, соевое, пальмоядровое и его фракции), эмульгатор моно- и диглицериды жирных кислот, антиокислитель концентрат смеси токоферолов, краситель бета-каротин), соль пищевая, соль-плавитель цитрат натрия, регулятор кислотности лимонная кислота, комплексные пищевые добавки «Аджика», «Сметана и лук», «Васаби», «Холодец с хреном» (соль, мальтодекстрин, глюкоза, овощи сушеные (томаты, чеснок, пастернак), усилитель вкуса и аромата (Е621, Е627, Е631), натуральные и идентичные натуральным вкусоароматические вещества, натуральные экстракты специй (лавровый лист, черный перец, тмин, кориандр), краситель «Маслосмолы паприки» (Е160с), сыворотка молочная, сахар, горчичный порошок, растительное масло, антиокислитель (Е300, Е306), регулятор кислотности (Е330, Е262), краситель (Е150с), агент антислеживающий (Е551))</t>
+  </si>
+  <si>
+    <t>сыр обезжиренный (молоко обезжиренное пастеризованное, закваска из чистых культур мезофильных молочнокислых микро-организмов, молокосвертывающий фермент (пепсин животного происхождения), уплотнитель - кальций хлористый), заменитель молочного жира (рафинированные дезодорированные растительные масла в натуральном и модифицированном виде (пальмовое и его фракции, подсолнечное, рапсовое, соевое, пальмоядровое и его фракции), эмульгатор моно- и диглицериды жирных кислот, антиокислитель концентрат смеси токоферолов, краситель бета-каротин), соль пищевая, соль-плавитель цитрат натрия, регулятор кислотности лимонная кислота, комплексные пищевые добавки «Аджика», «Холодец с хреном» (соль, мальтодекстрин, глюкоза, овощи сушеные (томаты, чеснок, пастернак), усилитель вкуса и аромата (Е621, Е627, Е631), натуральные и идентичные натуральным вкусоароматические вещества, натуральные экстракты специй (лавровый лист, черный перец, тмин, кориандр), краситель «Маслосмолы паприки» (Е160с), растительное масло, антиокислитель (Е300, Е306), регулятор кислотности (Е330, Е262), краситель (Е150с), агент антислеживающий (Е551).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,21 +299,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -313,65 +306,49 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="11">
@@ -493,8 +470,8 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
@@ -502,78 +479,86 @@
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="21" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="2" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="23">
@@ -861,400 +846,408 @@
   <dimension ref="A1:AE4"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="12"/>
-    <col min="2" max="2" width="14.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="2" customWidth="1"/>
-    <col min="5" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="2"/>
-    <col min="8" max="8" width="8.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="26.5703125" style="2" customWidth="1"/>
-    <col min="13" max="15" width="9.28515625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="2" customWidth="1"/>
-    <col min="18" max="20" width="9.28515625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="11.85546875" style="2" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="12" style="2" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="16.42578125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="14.140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="51.42578125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="30.28515625" style="26" customWidth="1"/>
-    <col min="29" max="29" width="30.5703125" style="2" customWidth="1"/>
-    <col min="30" max="30" width="22.5703125" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="8.7109375" style="2"/>
+    <col min="1" max="1" width="3.85546875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="11" style="14" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="18"/>
+    <col min="8" max="8" width="24.7109375" style="21" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="14" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" style="14" customWidth="1"/>
+    <col min="11" max="11" width="23" style="14" customWidth="1"/>
+    <col min="12" max="12" width="26.5703125" style="14" customWidth="1"/>
+    <col min="13" max="15" width="9.28515625" style="14" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" style="14" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="14" customWidth="1"/>
+    <col min="18" max="20" width="9.28515625" style="14" customWidth="1"/>
+    <col min="21" max="21" width="11.85546875" style="14" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="14" customWidth="1"/>
+    <col min="23" max="23" width="12" style="14" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="14" customWidth="1"/>
+    <col min="25" max="25" width="16.42578125" style="14" customWidth="1"/>
+    <col min="26" max="26" width="14.140625" style="14" customWidth="1"/>
+    <col min="27" max="27" width="51.42578125" style="14" customWidth="1"/>
+    <col min="28" max="28" width="30.28515625" style="19" customWidth="1"/>
+    <col min="29" max="29" width="38.28515625" style="14" customWidth="1"/>
+    <col min="30" max="30" width="31" style="14" customWidth="1"/>
+    <col min="31" max="31" width="113.140625" style="14" customWidth="1"/>
+    <col min="32" max="16384" width="8.7109375" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="17" customFormat="1" ht="47.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:31" s="4" customFormat="1" ht="75">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="18" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="V1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="18" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="18" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="18" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="18" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="18" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="24" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="18" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="18" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="18" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="85.5">
-      <c r="A2" s="11">
+    <row r="2" spans="1:31" ht="300">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="6">
         <v>2105201</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="9">
         <v>1901909900</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="5">
         <v>120</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="24">
         <v>4610043822840</v>
       </c>
-      <c r="L2" s="15">
+      <c r="L2" s="10">
         <v>14610043822847</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="5">
         <v>22</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="5">
         <v>10.3</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="5">
         <v>1.6</v>
       </c>
-      <c r="P2" s="23">
+      <c r="P2" s="11">
         <v>0.1</v>
       </c>
-      <c r="Q2" s="23">
+      <c r="Q2" s="11">
         <v>0.11</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="5">
         <v>38</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="5">
         <v>19</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="5">
         <v>13.5</v>
       </c>
-      <c r="U2" s="11">
+      <c r="U2" s="12">
         <v>24</v>
       </c>
-      <c r="V2" s="11">
+      <c r="V2" s="5">
         <v>2.4</v>
       </c>
-      <c r="W2" s="11">
+      <c r="W2" s="5">
         <v>8</v>
       </c>
-      <c r="X2" s="11">
+      <c r="X2" s="5">
         <v>18</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="Y2" s="5">
         <v>144</v>
       </c>
-      <c r="Z2" s="22">
+      <c r="Z2" s="13">
         <v>3456</v>
       </c>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC2" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE2" s="1"/>
+      <c r="AA2" s="8"/>
+      <c r="AB2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE2" s="27" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" ht="52.5">
-      <c r="A3" s="11">
+    <row r="3" spans="1:31" ht="281.25">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <v>2103201</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="9">
         <v>1901909900</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="5">
         <v>120</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="16">
         <v>4610043822871</v>
       </c>
       <c r="L3" s="16">
         <v>14610043822878</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="5">
         <v>22</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="5">
         <v>10.3</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="5">
         <v>1.6</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="5">
         <v>0.1</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="5">
         <v>0.11</v>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="5">
         <v>38</v>
       </c>
-      <c r="S3" s="11">
+      <c r="S3" s="5">
         <v>19</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="5">
         <v>13.5</v>
       </c>
-      <c r="U3" s="11">
+      <c r="U3" s="12">
         <v>24</v>
       </c>
-      <c r="V3" s="11">
+      <c r="V3" s="5">
         <v>2.4</v>
       </c>
-      <c r="W3" s="11">
+      <c r="W3" s="5">
         <v>8</v>
       </c>
-      <c r="X3" s="11">
+      <c r="X3" s="5">
         <v>18</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="Y3" s="5">
         <v>144</v>
       </c>
-      <c r="Z3" s="22">
+      <c r="Z3" s="13">
         <v>3456</v>
       </c>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD3" s="8" t="s">
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE3" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="93.75">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15">
+        <v>1103201</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" s="1"/>
-    </row>
-    <row r="4" spans="1:31" ht="54">
-      <c r="A4" s="11">
-        <v>3</v>
-      </c>
-      <c r="B4" s="14">
-        <v>1103201</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="5">
         <v>120</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="16">
         <v>4610043822901</v>
       </c>
       <c r="L4" s="16">
         <v>14610043822908</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="5">
         <v>9.6999999999999993</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="5">
         <v>9.5</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="5">
         <v>1.7</v>
       </c>
-      <c r="P4" s="11">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q4" s="11">
+      <c r="P4" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="Q4" s="5">
         <v>0.6</v>
       </c>
-      <c r="R4" s="11">
+      <c r="R4" s="5">
         <v>38</v>
       </c>
-      <c r="S4" s="11">
+      <c r="S4" s="5">
         <v>19</v>
       </c>
-      <c r="T4" s="11">
+      <c r="T4" s="5">
         <v>13.5</v>
       </c>
-      <c r="U4" s="11">
-        <v>36</v>
-      </c>
-      <c r="V4" s="11">
+      <c r="U4" s="12">
+        <v>24</v>
+      </c>
+      <c r="V4" s="5">
         <v>3</v>
       </c>
-      <c r="W4" s="11">
+      <c r="W4" s="5">
         <v>8</v>
       </c>
-      <c r="X4" s="11">
+      <c r="X4" s="5">
         <v>18</v>
       </c>
-      <c r="Y4" s="11">
+      <c r="Y4" s="5">
         <v>144</v>
       </c>
-      <c r="Z4" s="22">
-        <v>5184</v>
-      </c>
-      <c r="AA4" s="27" t="s">
+      <c r="Z4" s="25">
+        <v>3456</v>
+      </c>
+      <c r="AA4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AB4" s="25" t="s">
+      <c r="AC4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AC4" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE4" s="1"/>
+      <c r="AE4" s="20" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="27" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
